--- a/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
+++ b/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t xml:space="preserve">empresa</t>
   </si>
@@ -55,6 +55,18 @@
     <t xml:space="preserve">producto</t>
   </si>
   <si>
+    <t xml:space="preserve">facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competidor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competidor 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competidor 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acme SL</t>
   </si>
   <si>
@@ -76,6 +88,18 @@
     <t xml:space="preserve">servidores</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.facebook.com/acme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.competidor1.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.competidor2.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.competidor3.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tech Corp</t>
   </si>
   <si>
@@ -95,6 +119,9 @@
   </si>
   <si>
     <t xml:space="preserve">alta tecnologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.facebook.com/techcorp</t>
   </si>
 </sst>
 </file>
@@ -183,7 +210,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -196,7 +223,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -323,15 +354,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -347,7 +384,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -367,23 +404,35 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>6201</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>500</v>
@@ -395,30 +444,42 @@
         <v>500000</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>6201</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>100</v>
@@ -430,21 +491,35 @@
         <v>100000</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="4" t="s">
         <v>24</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="acme@acme.com"/>
     <hyperlink ref="E2" r:id="rId2" display="www.acme.com"/>
-    <hyperlink ref="D3" r:id="rId3" display="techcorp@techcorp.com"/>
-    <hyperlink ref="E3" r:id="rId4" display="www.techcorp.com"/>
+    <hyperlink ref="L2" r:id="rId3" display="https://www.facebook.com/acme"/>
+    <hyperlink ref="D3" r:id="rId4" display="techcorp@techcorp.com"/>
+    <hyperlink ref="E3" r:id="rId5" display="www.techcorp.com"/>
+    <hyperlink ref="L3" r:id="rId6" display="https://www.facebook.com/techcorp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
+++ b/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t xml:space="preserve">empresa</t>
   </si>
@@ -55,6 +55,12 @@
     <t xml:space="preserve">producto</t>
   </si>
   <si>
+    <t xml:space="preserve">provincia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pais</t>
+  </si>
+  <si>
     <t xml:space="preserve">facebook</t>
   </si>
   <si>
@@ -88,6 +94,12 @@
     <t xml:space="preserve">servidores</t>
   </si>
   <si>
+    <t xml:space="preserve">pontevedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">españa</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.facebook.com/acme</t>
   </si>
   <si>
@@ -119,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve">alta tecnologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lugo</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.facebook.com/techcorp</t>
@@ -354,10 +369,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.39"/>
@@ -365,10 +380,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="32.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="21.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="21.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -405,10 +422,10 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -416,23 +433,29 @@
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>6201</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>500</v>
@@ -444,42 +467,48 @@
         <v>500000</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="L2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="M2" s="0" t="s">
         <v>25</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>6201</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>100</v>
@@ -491,35 +520,41 @@
         <v>100000</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="acme@acme.com"/>
     <hyperlink ref="E2" r:id="rId2" display="www.acme.com"/>
-    <hyperlink ref="L2" r:id="rId3" display="https://www.facebook.com/acme"/>
+    <hyperlink ref="N2" r:id="rId3" display="https://www.facebook.com/acme"/>
     <hyperlink ref="D3" r:id="rId4" display="techcorp@techcorp.com"/>
     <hyperlink ref="E3" r:id="rId5" display="www.techcorp.com"/>
-    <hyperlink ref="L3" r:id="rId6" display="https://www.facebook.com/techcorp"/>
+    <hyperlink ref="N3" r:id="rId6" display="https://www.facebook.com/techcorp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
+++ b/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
@@ -20,57 +20,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
-  <si>
-    <t xml:space="preserve">empresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cnae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">web</t>
-  </si>
-  <si>
-    <t xml:space="preserve">numero_empleados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">telefono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facturacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vertical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">provincia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competidor 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competidor 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competidor 3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+  <si>
+    <t xml:space="preserve">Nombre empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIF empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero empleados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telefono empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facturacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provincia empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pais empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web competidor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook competidor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook competidor 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook competidor 3</t>
   </si>
   <si>
     <t xml:space="preserve">Acme SL</t>
@@ -100,7 +103,7 @@
     <t xml:space="preserve">españa</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.facebook.com/acme</t>
+    <t xml:space="preserve">www.facebook.com/acme</t>
   </si>
   <si>
     <t xml:space="preserve">www.competidor1.com</t>
@@ -112,6 +115,15 @@
     <t xml:space="preserve">www.competidor3.com</t>
   </si>
   <si>
+    <t xml:space="preserve">www.facebook.com/competidor1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.facebook.com/competidor2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.facebook.com/competidor3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tech Corp</t>
   </si>
   <si>
@@ -136,7 +148,7 @@
     <t xml:space="preserve">lugo</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.facebook.com/techcorp</t>
+    <t xml:space="preserve">www.facebook.com/techcorp</t>
   </si>
 </sst>
 </file>
@@ -146,7 +158,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -170,6 +182,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -181,6 +198,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -225,7 +255,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -238,11 +268,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -369,23 +419,28 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="32.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="21.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="27.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="28.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -422,10 +477,10 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -434,30 +489,39 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>6201</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="E2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G2" s="1" t="n">
@@ -467,50 +531,59 @@
         <v>500000</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="N2" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="O2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="P2" s="7" t="s">
         <v>29</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>6201</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="D3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>100</v>
       </c>
       <c r="G3" s="1" t="n">
@@ -520,41 +593,56 @@
         <v>100000</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="P3" s="7" t="s">
         <v>29</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="acme@acme.com"/>
     <hyperlink ref="E2" r:id="rId2" display="www.acme.com"/>
-    <hyperlink ref="N2" r:id="rId3" display="https://www.facebook.com/acme"/>
-    <hyperlink ref="D3" r:id="rId4" display="techcorp@techcorp.com"/>
-    <hyperlink ref="E3" r:id="rId5" display="www.techcorp.com"/>
-    <hyperlink ref="N3" r:id="rId6" display="https://www.facebook.com/techcorp"/>
+    <hyperlink ref="N2" r:id="rId3" display="www.facebook.com/acme"/>
+    <hyperlink ref="R2" r:id="rId4" display="www.facebook.com/competidor1"/>
+    <hyperlink ref="S2" r:id="rId5" display="www.facebook.com/competidor2"/>
+    <hyperlink ref="T2" r:id="rId6" display="www.facebook.com/competidor3"/>
+    <hyperlink ref="D3" r:id="rId7" display="techcorp@techcorp.com"/>
+    <hyperlink ref="E3" r:id="rId8" display="www.techcorp.com"/>
+    <hyperlink ref="N3" r:id="rId9" display="www.facebook.com/techcorp"/>
+    <hyperlink ref="R3" r:id="rId10" display="www.facebook.com/competidor1"/>
+    <hyperlink ref="S3" r:id="rId11" display="www.facebook.com/competidor2"/>
+    <hyperlink ref="T3" r:id="rId12" display="www.facebook.com/competidor3"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
+++ b/projecto_centralizar/frontend/public/templates/empresas_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t xml:space="preserve">Nombre empresa</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t xml:space="preserve">Web competidor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web competidor 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web competidor 3</t>
   </si>
   <si>
     <t xml:space="preserve">Facebook competidor 1</t>
@@ -158,7 +164,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -182,11 +188,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -198,19 +199,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -255,7 +243,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -264,35 +252,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -422,13 +390,13 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.49"/>
@@ -438,9 +406,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="20.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="27.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="28.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="28.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="27.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="28.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -490,38 +458,38 @@
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>6201</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>500</v>
       </c>
       <c r="G2" s="1" t="n">
@@ -531,59 +499,59 @@
         <v>500000</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="P2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="Q2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="R2" s="4" t="s">
         <v>33</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>6201</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="D3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G3" s="1" t="n">
@@ -593,40 +561,40 @@
         <v>100000</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="7" t="s">
+      <c r="N3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="P3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="Q3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="R3" s="4" t="s">
         <v>33</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
